--- a/artfynd/A 35916-2022 artfynd.xlsx
+++ b/artfynd/A 35916-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 35916-2022 artfynd.xlsx
+++ b/artfynd/A 35916-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94931412</v>
+        <v>94931478</v>
       </c>
       <c r="B2" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219955</v>
+        <v>208260</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>trafikdödad</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529972.8851597635</v>
+        <v>529973</v>
       </c>
       <c r="R2" t="n">
-        <v>6685234.175529246</v>
+        <v>6685234</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -756,24 +760,14 @@
           <t>2021-07-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-07-17</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>22 blombärande stjälkar samt ett antal sterila bladrosetter. Förhållandevis bra situation på lokalen - drog bort en del konkurrerande lingonris.</t>
+          <t>Låg överkörd på vägen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,7 +782,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Vägkant</t>
+          <t>Väg</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,56 +800,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94931478</v>
+        <v>98838937</v>
       </c>
       <c r="B3" t="n">
-        <v>57150</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208260</v>
+        <v>219955</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>trafikdödad</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -863,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529972.8851597635</v>
+        <v>529961</v>
       </c>
       <c r="R3" t="n">
-        <v>6685234.175529246</v>
+        <v>6685229</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -891,29 +875,19 @@
           <t>Silvberg</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>W-Sät-0040</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-07-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1989-01-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-07-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Låg överkörd på vägen</t>
+          <t>1989-01-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,52 +900,46 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Väg</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Staffan Jansson</t>
+          <t>Lennart Bratt</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Staffan Jansson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Sören Nyström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94931426</v>
+        <v>86572840</v>
       </c>
       <c r="B4" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220204</v>
+        <v>219955</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -981,15 +949,19 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -998,13 +970,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529972.8851597635</v>
+        <v>529960</v>
       </c>
       <c r="R4" t="n">
-        <v>6685234.175529246</v>
+        <v>6685237</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1028,22 +1000,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-07-17</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-07-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,23 +1018,505 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>89351101</v>
+      </c>
+      <c r="B5" t="n">
+        <v>107908</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bondhyttan, utmed vägen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>529960</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6685223</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Silvberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Inventering artrik vägkant Trafikverket</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lennart Sundh, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>94931412</v>
+      </c>
+      <c r="B6" t="n">
+        <v>107908</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bondhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>529973</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6685234</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Silvberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-07-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-07-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>22 blombärande stjälkar samt ett antal sterila bladrosetter. Förhållandevis bra situation på lokalen - drog bort en del konkurrerande lingonris.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Staffan Jansson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Staffan Jansson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>94931426</v>
+      </c>
+      <c r="B7" t="n">
+        <v>109815</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bondhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>529973</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6685234</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Silvberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-07-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-07-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Staffan Jansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Staffan Jansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127727117</v>
+      </c>
+      <c r="B8" t="n">
+        <v>109815</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bondhyttan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>529956</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6685225</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Silvberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Växer i ytterslänt.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Caroline Ahlgren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Caroline Ahlgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35916-2022 artfynd.xlsx
+++ b/artfynd/A 35916-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94931478</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -916,6 +926,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98838937</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1030,6 +1045,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86572840</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1150,6 +1170,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89351101</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1266,6 +1291,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94931412</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1381,6 +1411,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94931426</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1517,8 +1552,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127727117</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>